--- a/school_surveys/014_early_childhood_engagement_survey--school_surveys.xlsx
+++ b/school_surveys/014_early_childhood_engagement_survey--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Introduction to Survey</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>teacher_survey_section</t>
+          <t>parent_section</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Teacher Survey Section</t>
+          <t>Parent Survey Section</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>teacher_survey_question1</t>
+          <t>parent_survey_question1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Question 1</t>
+          <t>How often do you engage with your child's education?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>teacher_survey_question2</t>
+          <t>parent_survey_question2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Question 2</t>
+          <t>How would you rate the quality of your child's education?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>teacher_comments</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>teacher_survey_section2</t>
+          <t>teacher_section</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Teacher Survey Section 2</t>
+          <t>Teacher Survey Section</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>teacher_comments2</t>
+          <t>teacher_survey_question1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>How often do you engage with your child's teachers?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>teacher_survey_question1</t>
+          <t>teacher_survey_question2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Question 1</t>
+          <t>How supportive are you of your child's teacher?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>teacher_survey_question2</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Question 2</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>teacher_comments</t>
+          <t>school_section</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>School Survey Section</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>teacher_survey_section3</t>
+          <t>school_survey_question1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Teacher Survey Section 3</t>
+          <t>How would you rate the quality of your school?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>teacher_comments3</t>
+          <t>school_survey_question2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>How supportive is your school?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>teacher_comments4</t>
+          <t>comments_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>school_survey_section</t>
+          <t>school_comments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>School Survey Section</t>
+          <t>School Comments</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,251 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>school_comments</t>
+          <t>submission</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Submission</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>school_survey_question1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Question 1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>school_survey_question2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Question 2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>school_comments</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>school_survey_section2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>School Survey Section 2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>school_comments2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>school_survey_question1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Question 1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>school_survey_question2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Question 2</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>school_comments</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>school_comments2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,204 +896,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>teacher_survey_section_choices</t>
+          <t>parent_section_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>always_engaged</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Always Engaged</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>teacher_survey_section_choices</t>
+          <t>parent_section_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>sometimes_engaged</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Sometimes Engaged</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>teacher_survey_section_choices</t>
+          <t>parent_section_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>never_engaged</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Never Engaged</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>teacher_survey_question1_choices</t>
+          <t>parent_survey_question1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>almost_daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Almost Daily</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>teacher_survey_question1_choices</t>
+          <t>parent_survey_question1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>teacher_survey_question1_choices</t>
+          <t>parent_survey_question1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>teacher_survey_question2_choices</t>
+          <t>parent_survey_question2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>teacher_survey_question2_choices</t>
+          <t>parent_survey_question2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>teacher_survey_question2_choices</t>
+          <t>parent_survey_question2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>satisfactory</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>teacher_survey_section2_choices</t>
+          <t>teacher_section_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>always_available</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Always Available</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>teacher_survey_section2_choices</t>
+          <t>teacher_section_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>sometimes_available</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Sometimes Available</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>teacher_survey_section2_choices</t>
+          <t>teacher_section_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>rarely_available</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Rarely Available</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>almost_daily</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Almost Daily</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>very_supportive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Very Supportive</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>somewhat_supportive</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Somewhat Supportive</t>
         </is>
       </c>
     </row>
@@ -1420,420 +1190,216 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>not_supportive_at_all</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Not Supportive at All</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>teacher_survey_section3_choices</t>
+          <t>school_section_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>teacher_survey_section3_choices</t>
+          <t>school_section_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>teacher_survey_section3_choices</t>
+          <t>school_section_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>school_survey_section_choices</t>
+          <t>school_survey_question1_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>5-star</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>5-Star</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>school_survey_section_choices</t>
+          <t>school_survey_question1_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>4-star</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>4-Star</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>school_survey_section_choices</t>
+          <t>school_survey_question1_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>3-star</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>3-Star</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>school_survey_question1_choices</t>
+          <t>school_survey_question2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>very_supportive</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Very Supportive</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>school_survey_question1_choices</t>
+          <t>school_survey_question2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>somewhat_supportive</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Somewhat Supportive</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>school_survey_question1_choices</t>
+          <t>school_survey_question2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>not_supportive_at_all</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Not Supportive at All</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>school_survey_question2_choices</t>
+          <t>submission_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>school_survey_question2_choices</t>
+          <t>submission_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>save_and_resume_later</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Save and Resume Later</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>school_survey_question2_choices</t>
+          <t>submission_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>do_not_submit</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>school_survey_section2_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>school_survey_section2_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>school_survey_section2_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>school_survey_question1_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>school_survey_question1_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>school_survey_question1_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>school_survey_question2_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>school_survey_question2_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>school_survey_question2_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Do Not Submit</t>
         </is>
       </c>
     </row>
